--- a/data/trans_orig/P32D_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32D_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses ha tomado 6/5 (Hombre/Mujer) o más bebidas estándar en una misma ocasión en 2023</t>
+          <t>Población según si en los últimos 12 meses ha tomado 6/5 (Hombre/Mujer) o más bebidas estándar en una misma ocasión en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34756</t>
+          <t>33903</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79808</t>
+          <t>80928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30103</t>
+          <t>31118</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55774</t>
+          <t>57114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72484</t>
+          <t>72034</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124352</t>
+          <t>125468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,34%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26485</t>
+          <t>26609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63097</t>
+          <t>62238</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26518</t>
+          <t>25315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40331</t>
+          <t>39478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80820</t>
+          <t>81761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52213</t>
+          <t>52767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36511</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38251</t>
+          <t>38412</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79748</t>
+          <t>79064</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31742</t>
+          <t>31677</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>338</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34971</t>
+          <t>34692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25307</t>
+          <t>26854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16048</t>
+          <t>15416</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33539</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>21414</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33375</t>
+          <t>31474</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -1408,97 +1408,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2082</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4582</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7477</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2082</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7587</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2082</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6785</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2840</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>7092</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1554</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>7286</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,62 +1669,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2906</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2840</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>9143</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2906</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>9610</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27301</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60578</t>
+          <t>61674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30998</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53749</t>
+          <t>53465</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66328</t>
+          <t>63938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105656</t>
+          <t>102904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54871</t>
+          <t>54851</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92100</t>
+          <t>90797</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33509</t>
+          <t>34044</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55647</t>
+          <t>57254</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>96986</t>
+          <t>96386</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>139241</t>
+          <t>140257</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52200</t>
+          <t>52306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87965</t>
+          <t>85677</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23810</t>
+          <t>24357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46753</t>
+          <t>45022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80672</t>
+          <t>81946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123621</t>
+          <t>123973</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37092</t>
+          <t>36342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>17139</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>19609</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48244</t>
+          <t>48328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26392</t>
+          <t>27491</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>18249</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37839</t>
+          <t>36823</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15414</t>
+          <t>14664</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -2542,97 +2542,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2827</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2655,97 +2655,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>2827</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,62 +2803,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4817</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>859</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3569</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28521</t>
+          <t>29525</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52566</t>
+          <t>53855</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49809</t>
+          <t>49313</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>68905</t>
+          <t>69752</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>83086</t>
+          <t>84038</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>116504</t>
+          <t>117490</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97353</t>
+          <t>98224</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133784</t>
+          <t>133958</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52327</t>
+          <t>52069</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72256</t>
+          <t>72042</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>155390</t>
+          <t>156939</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196695</t>
+          <t>197642</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61420</t>
+          <t>61883</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>94277</t>
+          <t>93858</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28740</t>
+          <t>28181</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>79685</t>
+          <t>80391</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116830</t>
+          <t>115360</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15132</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>34357</t>
+          <t>33371</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>39618</t>
+          <t>37508</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23962</t>
+          <t>23781</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26368</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>20938</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>974</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -3789,97 +3789,97 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>1663</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3902,62 +3902,62 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>5894</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>3009</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>66173</t>
+          <t>66476</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>99715</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>67222</t>
+          <t>67244</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>87579</t>
+          <t>87410</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>139957</t>
+          <t>140162</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>179696</t>
+          <t>177994</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>128244</t>
+          <t>128989</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>169947</t>
+          <t>168214</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>59509</t>
+          <t>59299</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>80247</t>
+          <t>79503</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4315,12 +4315,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>195795</t>
+          <t>198076</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>241528</t>
+          <t>240823</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>49359</t>
+          <t>49433</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>78471</t>
+          <t>78182</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>20950</t>
+          <t>21219</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>37538</t>
+          <t>37380</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>76841</t>
+          <t>76031</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>110311</t>
+          <t>108281</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>51350</t>
+          <t>57261</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>59617</t>
+          <t>63124</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4584,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4697,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>22844</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>25762</t>
+          <t>24681</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4845,62 +4845,62 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>1135</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>3577</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>5805</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -4923,97 +4923,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>1135</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>1562</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -5266,12 +5266,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>35462</t>
+          <t>35902</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>58490</t>
+          <t>58478</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>58645</t>
+          <t>59214</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>76491</t>
+          <t>76079</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>99353</t>
+          <t>98615</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>129529</t>
+          <t>130690</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -5379,12 +5379,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>103534</t>
+          <t>104808</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>133941</t>
+          <t>134605</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>47713</t>
+          <t>47448</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5449,12 +5449,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>142179</t>
+          <t>141529</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>177093</t>
+          <t>177425</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -5492,12 +5492,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>37043</t>
+          <t>37662</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>61615</t>
+          <t>61642</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>22301</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>52704</t>
+          <t>52373</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>78214</t>
+          <t>78522</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>34067</t>
+          <t>35349</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>20187</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>39846</t>
+          <t>39492</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5733,12 +5733,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>505</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>13144</t>
+          <t>13521</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -5831,12 +5831,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>526</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -5944,12 +5944,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6057,12 +6057,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6142,12 +6142,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -6400,12 +6400,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>40383</t>
+          <t>40170</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>59571</t>
+          <t>59276</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>147419</t>
+          <t>144713</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>272753</t>
+          <t>272664</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>155091</t>
+          <t>152674</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>407206</t>
+          <t>409617</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6485,12 +6485,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6513,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>76920</t>
+          <t>77427</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>98053</t>
+          <t>99038</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>91827</t>
+          <t>95090</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>39224</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>207262</t>
+          <t>204755</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -6626,12 +6626,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>19850</t>
+          <t>20221</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>35994</t>
+          <t>34988</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>60851</t>
+          <t>61908</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>11602</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>23676</t>
+          <t>25042</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>755</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -7078,12 +7078,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>437</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -7191,97 +7191,97 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="R61" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>3512</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T61" s="2" t="inlineStr">
-        <is>
-          <t>2053</t>
-        </is>
-      </c>
-      <c r="U61" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>298</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>25292</t>
+          <t>25393</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>39776</t>
+          <t>39239</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>17936</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>54800</t>
+          <t>55165</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -7647,12 +7647,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>42704</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>58232</t>
+          <t>58847</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>50250</t>
+          <t>48986</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>67184</t>
+          <t>66047</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -7873,12 +7873,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7888,12 +7888,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8021,62 +8021,62 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>4013</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>1151</t>
-        </is>
-      </c>
-      <c r="S68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T68" s="2" t="inlineStr">
-        <is>
-          <t>4193</t>
-        </is>
-      </c>
-      <c r="U68" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V68" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>991</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8134,62 +8134,62 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="S69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T69" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
-      <c r="U69" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V69" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -8212,97 +8212,97 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>1153</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="R70" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T70" s="2" t="inlineStr">
-        <is>
-          <t>1103</t>
-        </is>
-      </c>
-      <c r="U70" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8360,62 +8360,62 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>6122</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R71" s="2" t="inlineStr">
-        <is>
-          <t>1094</t>
-        </is>
-      </c>
-      <c r="S71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T71" s="2" t="inlineStr">
-        <is>
-          <t>6094</t>
-        </is>
-      </c>
-      <c r="U71" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V71" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -8438,12 +8438,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -8668,12 +8668,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>309402</t>
+          <t>307992</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>388854</t>
+          <t>387547</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>419980</t>
+          <t>422717</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>758170</t>
+          <t>751416</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>729855</t>
+          <t>733316</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>1312763</t>
+          <t>1398915</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>591606</t>
+          <t>592431</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>677629</t>
+          <t>681719</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>146035</t>
+          <t>148682</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>336124</t>
+          <t>336556</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8831,12 +8831,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>687339</t>
+          <t>657914</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>993364</t>
+          <t>997132</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8866,12 +8866,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -8894,12 +8894,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>293663</t>
+          <t>293479</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>366923</t>
+          <t>366401</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8909,12 +8909,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>68093</t>
+          <t>75521</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>170117</t>
+          <t>168930</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8944,12 +8944,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>337885</t>
+          <t>324634</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>515023</t>
+          <t>508338</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8979,12 +8979,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -9007,12 +9007,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>94259</t>
+          <t>93262</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>153133</t>
+          <t>153409</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9042,12 +9042,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>42022</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9057,12 +9057,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9077,12 +9077,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>110020</t>
+          <t>108593</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>180423</t>
+          <t>180258</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>45328</t>
+          <t>46504</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>82586</t>
+          <t>81747</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>40107</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9170,12 +9170,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>63503</t>
+          <t>63380</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>111173</t>
+          <t>109674</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -9233,12 +9233,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>37933</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>68484</t>
+          <t>68339</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9268,12 +9268,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9303,12 +9303,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>53246</t>
+          <t>53457</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>95882</t>
+          <t>93757</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -9346,12 +9346,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -9459,12 +9459,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>34160</t>
+          <t>33648</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32D_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32D_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>54227</t>
+          <t>45651</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>28064</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80928</t>
+          <t>70144</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43008</t>
+          <t>45106</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31118</t>
+          <t>31691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57114</t>
+          <t>59602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>97235</t>
+          <t>90757</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72034</t>
+          <t>67696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125468</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42445</t>
+          <t>45174</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26609</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62238</t>
+          <t>63221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>17288</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>28656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58272</t>
+          <t>62462</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39478</t>
+          <t>44311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81761</t>
+          <t>84889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33023</t>
+          <t>32138</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18283</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52767</t>
+          <t>50680</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23519</t>
+          <t>26228</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>15396</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>39741</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56543</t>
+          <t>58367</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38412</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79064</t>
+          <t>82055</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14565</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31677</t>
+          <t>28104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34692</t>
+          <t>35748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26854</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>22008</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32323</t>
+          <t>41650</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21414</t>
+          <t>24362</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17434</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31474</t>
+          <t>36465</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>11214</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -1742,17 +1742,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42091</t>
+          <t>41387</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>60166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41106</t>
+          <t>44303</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>33212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53465</t>
+          <t>56446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>83197</t>
+          <t>85690</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63938</t>
+          <t>65119</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102904</t>
+          <t>104769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72683</t>
+          <t>78329</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54851</t>
+          <t>62448</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90797</t>
+          <t>99766</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44590</t>
+          <t>47225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34044</t>
+          <t>35537</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57254</t>
+          <t>60443</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>117272</t>
+          <t>125554</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>96386</t>
+          <t>104118</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>140257</t>
+          <t>148151</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>68649</t>
+          <t>76881</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52306</t>
+          <t>59706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85677</t>
+          <t>97575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>33608</t>
+          <t>35155</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24357</t>
+          <t>25751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45022</t>
+          <t>47946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>102257</t>
+          <t>112035</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81946</t>
+          <t>92711</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123973</t>
+          <t>137695</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>23450</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12113</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36342</t>
+          <t>38728</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17139</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>31493</t>
+          <t>33786</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19609</t>
+          <t>21978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48328</t>
+          <t>50309</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27491</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18249</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>29787</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14428</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36823</t>
+          <t>45939</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -2424,32 +2424,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>14514</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2459,32 +2459,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>910</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2773,12 +2773,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>910</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>228470</t>
+          <t>247971</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228470</t>
+          <t>247971</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>228470</t>
+          <t>247971</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>370723</t>
+          <t>400962</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>370723</t>
+          <t>400962</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>370723</t>
+          <t>400962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40030</t>
+          <t>41846</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29525</t>
+          <t>31342</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53855</t>
+          <t>57230</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>59128</t>
+          <t>63460</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49313</t>
+          <t>53665</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69752</t>
+          <t>74391</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>99158</t>
+          <t>105306</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>84038</t>
+          <t>89251</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>117490</t>
+          <t>121321</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -3106,32 +3106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>114897</t>
+          <t>129454</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98224</t>
+          <t>108519</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133958</t>
+          <t>147517</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3141,32 +3141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>62049</t>
+          <t>69288</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52069</t>
+          <t>59226</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72042</t>
+          <t>81333</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3176,32 +3176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>176946</t>
+          <t>198743</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>156939</t>
+          <t>176061</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>197642</t>
+          <t>219382</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -3219,102 +3219,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>77057</t>
+          <t>85714</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61883</t>
+          <t>71127</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93858</t>
+          <t>105962</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>27,4%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>22,74%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>33,88%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>25404</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>17919</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>33973</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>14,95%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>111118</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>93760</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>131809</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>23,02%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>19,42%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>27,31%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>21,93%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>33,26%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>20845</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>14533</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>28181</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>13,82%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>9,64%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>18,69%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>97902</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>80391</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>115360</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>18,57%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -3332,32 +3332,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>23342</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33371</t>
+          <t>37861</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3367,32 +3367,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3402,32 +3402,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>26682</t>
+          <t>31279</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>37508</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -3445,32 +3445,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23781</t>
+          <t>23588</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,22 +3480,22 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>791</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>17438</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>27544</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19255</t>
+          <t>20548</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3593,32 +3593,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20938</t>
+          <t>22693</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>736</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3897,32 +3897,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>806</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,32 +3967,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>807</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4010,17 +4010,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4080,17 +4080,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4127,32 +4127,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>82108</t>
+          <t>85114</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>66476</t>
+          <t>68992</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>101975</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4162,32 +4162,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>77172</t>
+          <t>82889</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>67244</t>
+          <t>72195</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>87410</t>
+          <t>94141</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>159280</t>
+          <t>168002</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>140162</t>
+          <t>148139</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>177994</t>
+          <t>190902</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -4240,102 +4240,102 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>150189</t>
+          <t>157496</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>128989</t>
+          <t>138909</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>168214</t>
+          <t>176088</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
+          <t>39,26%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>49,77%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>76476</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>66736</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>88945</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>36,44%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>31,8%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>42,38%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>233972</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>211897</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>255173</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>41,51%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
           <t>37,59%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>49,01%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>69391</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>59299</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>79503</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>36,56%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>31,24%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>41,89%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>219580</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>198076</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>240823</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>41,2%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>37,16%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,27%</t>
         </is>
       </c>
     </row>
@@ -4353,32 +4353,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>63134</t>
+          <t>67607</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>49433</t>
+          <t>54232</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>78182</t>
+          <t>84771</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4388,32 +4388,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>28272</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>21219</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>37380</t>
+          <t>42129</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4423,32 +4423,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>91406</t>
+          <t>100565</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>76031</t>
+          <t>83014</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>108281</t>
+          <t>118290</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -4466,32 +4466,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>57261</t>
+          <t>21946</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4501,32 +4501,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10827</t>
+          <t>12816</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4536,32 +4536,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>26100</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>63124</t>
+          <t>29327</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -4579,32 +4579,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4614,32 +4614,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4649,32 +4649,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>18090</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>22976</t>
+          <t>27270</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -4692,32 +4692,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4727,32 +4727,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4762,32 +4762,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9877</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>24681</t>
+          <t>26623</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>810</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>810</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5031,32 +5031,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,32 +5101,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -5144,17 +5144,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>343191</t>
+          <t>353838</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>343191</t>
+          <t>353838</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>343191</t>
+          <t>353838</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,17 +5179,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>189801</t>
+          <t>209856</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>189801</t>
+          <t>209856</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>189801</t>
+          <t>209856</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>532992</t>
+          <t>563694</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>532992</t>
+          <t>563694</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>532992</t>
+          <t>563694</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>46303</t>
+          <t>48888</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>35902</t>
+          <t>37387</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>58478</t>
+          <t>61609</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5296,32 +5296,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>67638</t>
+          <t>72258</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>59214</t>
+          <t>63152</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>76079</t>
+          <t>81418</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5331,32 +5331,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>113941</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>98615</t>
+          <t>105187</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>130690</t>
+          <t>138516</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -5374,32 +5374,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>118932</t>
+          <t>123926</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>104808</t>
+          <t>108787</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>134605</t>
+          <t>140175</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5409,32 +5409,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>39727</t>
+          <t>44859</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>32323</t>
+          <t>37403</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>47448</t>
+          <t>54154</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5444,32 +5444,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>158659</t>
+          <t>168785</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>141529</t>
+          <t>151057</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>177425</t>
+          <t>188123</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -5487,32 +5487,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>48883</t>
+          <t>57293</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>37662</t>
+          <t>45381</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>61642</t>
+          <t>71396</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5522,32 +5522,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>15947</t>
+          <t>18339</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>22992</t>
+          <t>25168</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>64830</t>
+          <t>75632</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>52373</t>
+          <t>60890</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>78522</t>
+          <t>90594</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -5600,32 +5600,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>24727</t>
+          <t>25661</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>16487</t>
+          <t>17517</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>35349</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5635,32 +5635,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>30345</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>20646</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>39492</t>
+          <t>41773</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -5713,32 +5713,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11836</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5748,32 +5748,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>526</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -5826,32 +5826,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>14754</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5896,32 +5896,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -5939,32 +5939,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6009,32 +6009,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -6057,27 +6057,27 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6127,27 +6127,27 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>993</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -6165,32 +6165,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>942</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6278,17 +6278,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>261562</t>
+          <t>279007</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>261562</t>
+          <t>279007</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>261562</t>
+          <t>279007</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6313,17 +6313,17 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>133678</t>
+          <t>146852</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>133678</t>
+          <t>146852</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>133678</t>
+          <t>146852</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6348,17 +6348,17 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>395240</t>
+          <t>425859</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>395240</t>
+          <t>425859</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>395240</t>
+          <t>425859</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6395,32 +6395,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>49197</t>
+          <t>54988</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>40170</t>
+          <t>44864</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>59276</t>
+          <t>65254</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6430,32 +6430,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>246193</t>
+          <t>42626</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>144713</t>
+          <t>35537</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>272664</t>
+          <t>49335</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6465,32 +6465,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>295389</t>
+          <t>97614</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>152674</t>
+          <t>85106</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>409617</t>
+          <t>110836</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -6508,32 +6508,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>88013</t>
+          <t>94598</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>77427</t>
+          <t>83913</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>99038</t>
+          <t>107370</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6543,32 +6543,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>25857</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>95090</t>
+          <t>31984</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6578,32 +6578,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>111221</t>
+          <t>120455</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>106641</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>204755</t>
+          <t>133877</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -6621,32 +6621,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>27492</t>
+          <t>30529</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>20221</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>34988</t>
+          <t>39329</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6656,32 +6656,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>21134</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6691,32 +6691,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>27865</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>61908</t>
+          <t>46235</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -6734,32 +6734,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>17006</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6769,32 +6769,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>11602</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6804,32 +6804,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>11714</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>20152</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -6847,32 +6847,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>612</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6917,32 +6917,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -6960,22 +6960,22 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6995,32 +6995,32 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7030,32 +7030,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -7073,32 +7073,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>421</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>462</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -7118,57 +7118,57 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>5105</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="inlineStr">
-        <is>
-          <t>5962</t>
-        </is>
-      </c>
-      <c r="U60" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -7299,32 +7299,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -7412,17 +7412,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>187196</t>
+          <t>204875</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>187196</t>
+          <t>204875</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>187196</t>
+          <t>204875</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7447,17 +7447,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>280153</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>280153</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>280153</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7482,17 +7482,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>467348</t>
+          <t>285687</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>467348</t>
+          <t>285687</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>467348</t>
+          <t>285687</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7529,32 +7529,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>31792</t>
+          <t>33825</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>39239</t>
+          <t>41999</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7564,32 +7564,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>14493</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>17936</t>
+          <t>19410</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7599,32 +7599,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>46285</t>
+          <t>49157</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>39814</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>55165</t>
+          <t>58162</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>41,92%</t>
         </is>
       </c>
     </row>
@@ -7642,32 +7642,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>50669</t>
+          <t>55841</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>42898</t>
+          <t>47674</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>58847</t>
+          <t>63696</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7677,32 +7677,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>58068</t>
+          <t>64993</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>48986</t>
+          <t>56317</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>74924</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -7755,32 +7755,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>15687</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7790,32 +7790,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7825,32 +7825,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>18892</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -7868,32 +7868,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7938,32 +7938,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>858</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>858</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
@@ -8433,32 +8433,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8503,32 +8503,32 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -8546,17 +8546,17 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>107879</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>107879</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>107879</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>30878</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>30878</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>30878</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8616,17 +8616,17 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>125359</t>
+          <t>138758</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>125359</t>
+          <t>138758</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>125359</t>
+          <t>138758</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8663,32 +8663,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>345748</t>
+          <t>351699</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>307992</t>
+          <t>316305</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>387547</t>
+          <t>393846</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8698,32 +8698,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>548737</t>
+          <t>365973</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>422717</t>
+          <t>336674</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>751416</t>
+          <t>391794</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8733,32 +8733,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>894485</t>
+          <t>717672</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>733316</t>
+          <t>671430</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>1398915</t>
+          <t>764239</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -8776,32 +8776,32 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>637828</t>
+          <t>684819</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>592431</t>
+          <t>637074</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>681719</t>
+          <t>729414</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8811,32 +8811,32 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>262191</t>
+          <t>290144</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>265998</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>336556</t>
+          <t>314606</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8846,32 +8846,32 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>900019</t>
+          <t>974964</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>657914</t>
+          <t>924903</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>997132</t>
+          <t>1024075</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,74%</t>
         </is>
       </c>
     </row>
@@ -8889,32 +8889,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>326676</t>
+          <t>359318</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>293479</t>
+          <t>321521</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>366401</t>
+          <t>397613</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8924,32 +8924,32 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>129762</t>
+          <t>147412</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>75521</t>
+          <t>125658</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>168930</t>
+          <t>169337</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8959,32 +8959,32 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>456438</t>
+          <t>506730</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>324634</t>
+          <t>462763</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>508338</t>
+          <t>545200</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -9002,32 +9002,32 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>116683</t>
+          <t>115279</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>93262</t>
+          <t>94295</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>153409</t>
+          <t>140892</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9037,32 +9037,32 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>28964</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>25681</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>42022</t>
+          <t>49706</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9072,32 +9072,32 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>145647</t>
+          <t>151728</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>108593</t>
+          <t>126411</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>180258</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -9115,32 +9115,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>61524</t>
+          <t>73362</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>46504</t>
+          <t>56476</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>81747</t>
+          <t>96467</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9150,32 +9150,32 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>25222</t>
+          <t>27966</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>38885</t>
+          <t>41932</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9185,32 +9185,32 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>86746</t>
+          <t>101329</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>82515</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>109674</t>
+          <t>126459</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -9228,32 +9228,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>51811</t>
+          <t>55075</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>41762</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>68339</t>
+          <t>75899</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9263,32 +9263,32 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>32913</t>
+          <t>39184</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9298,32 +9298,32 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>72673</t>
+          <t>80784</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>53457</t>
+          <t>63230</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>93757</t>
+          <t>103405</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -9341,32 +9341,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9376,32 +9376,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9411,32 +9411,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -9454,32 +9454,32 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9524,32 +9524,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -9567,32 +9567,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9602,32 +9602,32 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9637,32 +9637,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>26187</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>33648</t>
+          <t>38236</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -9680,17 +9680,17 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9715,17 +9715,17 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9750,17 +9750,17 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
